--- a/untranslated/downloads/data-excel/15.1.2.1.xlsx
+++ b/untranslated/downloads/data-excel/15.1.2.1.xlsx
@@ -516,7 +516,7 @@
     <col min="6" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -529,7 +529,7 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>9</v>
       </c>
@@ -540,7 +540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -553,7 +553,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
@@ -593,8 +593,14 @@
       <c r="M4" s="4">
         <v>2021</v>
       </c>
+      <c r="N4" s="4">
+        <v>2022</v>
+      </c>
+      <c r="O4" s="4">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
@@ -632,6 +638,12 @@
         <v>6.53</v>
       </c>
       <c r="M5" s="5">
+        <v>6.53</v>
+      </c>
+      <c r="N5" s="5">
+        <v>6.53</v>
+      </c>
+      <c r="O5" s="5">
         <v>6.53</v>
       </c>
     </row>
